--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20261014.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20261014.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>58,646,889</t>
+          <t>17,032,550</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>17,032,550</t>
+          <t>58,646,889</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>33,091,866</t>
+          <t>28,871,053</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>28,871,053</t>
+          <t>33,091,866</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
